--- a/output/2026-09-06_06_Slovenia_Savinjska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-06_06_Slovenia_Savinjska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tecnica trgovina na debelo in drobno, Opekarniška cesta 2, Celje, dal 1990. Vende anche utensili e macchine utensili.</t>
+          <t>Tecnica trgovina na debelo in drobno, Opekarniška cesta 2, Celje, dal 1990. Vende anche utensili e macchine utensili. [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -516,7 +516,6 @@
           <t>GRR d.o.o. (inženiring in vzdrževanje)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Griže (comune di Žalec)</t>
@@ -527,8 +526,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Noleggio e assistenza macchine per la lavorazione, sede Griže 5. Nessun sito ufficiale/telefono/email pubblici trovati.</t>
@@ -692,7 +689,6 @@
           <t>070 825 309</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Negozio di utensili (trgovina z orodjem), Ulica Janka Ulriha 1, Velenje.</t>
@@ -809,8 +805,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Punto vendita autorizzato Villager, Liptovska cesta 8, Slovenske Konjice, tra i dealer ufficiali elencati.</t>

--- a/output/2026-09-06_06_Slovenia_Savinjska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-06_06_Slovenia_Savinjska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
